--- a/contacts/Test_Terminagent.xlsx
+++ b/contacts/Test_Terminagent.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Nachname</t>
   </si>
@@ -34,7 +34,10 @@
     <t>Meier</t>
   </si>
   <si>
-    <t>Miriam</t>
+    <t>Karian</t>
+  </si>
+  <si>
+    <t>+4915783873559</t>
   </si>
   <si>
     <t>Weber</t>
@@ -454,35 +457,37 @@
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/contacts/Test_Terminagent.xlsx
+++ b/contacts/Test_Terminagent.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Nachname</t>
   </si>
@@ -28,7 +28,10 @@
     <t>Huber</t>
   </si>
   <si>
-    <t>Klaus</t>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>+40189562467</t>
   </si>
   <si>
     <t>Meier</t>
@@ -448,46 +451,48 @@
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/contacts/Test_Terminagent.xlsx
+++ b/contacts/Test_Terminagent.xlsx
@@ -28,10 +28,10 @@
     <t>Huber</t>
   </si>
   <si>
-    <t>Mark</t>
-  </si>
-  <si>
-    <t>+40189562467</t>
+    <t>Liam</t>
+  </si>
+  <si>
+    <t>+491794230153</t>
   </si>
   <si>
     <t>Meier</t>

--- a/contacts/Test_Terminagent.xlsx
+++ b/contacts/Test_Terminagent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rson\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF8D76A0-BB29-4C08-ACB4-B8044A20A664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D36756AD-3324-4B3A-94CA-F9047B22547C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3072" yWindow="3072" windowWidth="17280" windowHeight="9960" xr2:uid="{6096A44A-51A0-4B86-82A8-8E25DE3E4635}"/>
   </bookViews>
@@ -142,10 +142,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -511,6 +507,9 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
+      <c r="C4">
+        <v>491742418011</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -519,6 +518,9 @@
       <c r="B5" t="s">
         <v>8</v>
       </c>
+      <c r="C5">
+        <v>491742418011</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -548,20 +550,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9417af3b-7a6f-4a38-86da-08a3be6e98b1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9417af3b-7a6f-4a38-86da-08a3be6e98b1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -741,14 +743,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08FF2DF0-47E4-4133-9213-1A77E4FA1C73}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB30B65-2733-4DE9-9DBF-3FF31C918487}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -760,6 +754,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08FF2DF0-47E4-4133-9213-1A77E4FA1C73}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/contacts/Test_Terminagent.xlsx
+++ b/contacts/Test_Terminagent.xlsx
@@ -1,93 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Tabelle1"/>
+    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>Nachname</t>
-  </si>
-  <si>
-    <t>Vorname</t>
-  </si>
-  <si>
-    <t>Nummer</t>
-  </si>
-  <si>
-    <t>Huber</t>
-  </si>
-  <si>
-    <t>Liam</t>
-  </si>
-  <si>
-    <t>+491794230153</t>
-  </si>
-  <si>
-    <t>Meier</t>
-  </si>
-  <si>
-    <t>Karian</t>
-  </si>
-  <si>
-    <t>+4915783873559</t>
-  </si>
-  <si>
-    <t>Weber</t>
-  </si>
-  <si>
-    <t>Otto</t>
-  </si>
-  <si>
-    <t>Seitz</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>Haas</t>
-  </si>
-  <si>
-    <t>Joel</t>
-  </si>
-  <si>
-    <t>+491742418011</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -110,30 +57,92 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -421,78 +430,141 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="18.14785714285714" customWidth="1" bestFit="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="18.14785714285714" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nachname</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Vorname</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nummer</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Anrede</t>
+        </is>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Huber</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>+491794230153</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Meier</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Karian</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>+4915783873559</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Weber</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Otto</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
+      </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2"/>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Seitz</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
+      </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Haas</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>+491742418011</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
       </c>
     </row>
   </sheetData>
